--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487760_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487760_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5297</v>
+        <v>4.738</v>
       </c>
       <c r="E2" t="n">
-        <v>7.029</v>
+        <v>7.2667</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.4993</v>
+        <v>-2.5287</v>
       </c>
       <c r="G2" t="n">
         <v>2.649</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1659</v>
+        <v>-0.9576</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2676</v>
+        <v>-0.0299</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8983</v>
+        <v>-0.9277</v>
       </c>
       <c r="V2" t="n">
         <v>2.006</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1624</v>
+        <v>0.299</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.1072</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1624</v>
+        <v>0.1918</v>
       </c>
       <c r="G3" t="n">
         <v>0.1429</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0196</v>
+        <v>0.1561</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.1072</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3712</v>
+        <v>-0.5202</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5173</v>
+        <v>-0.6664</v>
       </c>
       <c r="F4" t="n">
         <v>0.1461</v>
@@ -766,10 +766,10 @@
         <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0405</v>
+        <v>-0.1895</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0619</v>
+        <v>-0.0871</v>
       </c>
       <c r="U4" t="n">
         <v>-0.1024</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.8948</v>
+        <v>-1.7099</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2811</v>
+        <v>-0.0668</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6137</v>
+        <v>-1.6431</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0211</v>
@@ -844,13 +844,13 @@
         <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9173</v>
+        <v>-0.7323</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6524</v>
+        <v>-0.4381</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2649</v>
+        <v>-0.2942</v>
       </c>
       <c r="V5" t="n">
         <v>-0.789</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.8831</v>
+        <v>-2.9646</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0985</v>
+        <v>0.1637</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.9816</v>
+        <v>-3.1284</v>
       </c>
       <c r="G6" t="n">
         <v>-3.5462</v>
@@ -922,13 +922,13 @@
         <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0484</v>
+        <v>-1.13</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0718</v>
+        <v>-0.0066</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9766</v>
+        <v>-1.1234</v>
       </c>
       <c r="V6" t="n">
         <v>0.2547</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.0423</v>
+        <v>-3.1286</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3418</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7005</v>
+        <v>-2.495</v>
       </c>
       <c r="G7" t="n">
         <v>-3.033</v>
@@ -1000,13 +1000,13 @@
         <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6336</v>
+        <v>-0.7199</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9134</v>
+        <v>-0.2052</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7202</v>
+        <v>-0.5147</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. YARNOZ LUMBRERAS</t>
+          <t>J. DJERY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.8576</v>
+        <v>-5.8648</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3816</v>
+        <v>-3.6143</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.476</v>
+        <v>-2.2505</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.743</v>
+        <v>-4.4456</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.1109</v>
+        <v>-2.7442</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.632</v>
+        <v>-1.7014</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3503</v>
+        <v>-1.988</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.4206</v>
+        <v>-2.0664</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0703</v>
+        <v>0.0784</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.3927</v>
+        <v>-2.4576</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6904</v>
+        <v>-0.6778</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.7023</v>
+        <v>-1.7798</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4974</v>
+        <v>-1.2487</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2893</v>
+        <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6525</v>
+        <v>-0.2517</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5899</v>
+        <v>-0.3776</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9374</v>
+        <v>0.1259</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-1.1675</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1238</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4352</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. DJERY</t>
+          <t>P. YARNOZ LUMBRERAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.4724</v>
+        <v>-6.8512</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2806</v>
+        <v>-3.2871</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1918</v>
+        <v>-3.5641</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.4456</v>
+        <v>-5.743</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.7442</v>
+        <v>-4.1109</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7014</v>
+        <v>-1.632</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.988</v>
+        <v>-1.3503</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.0664</v>
+        <v>-2.4206</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0784</v>
+        <v>1.0703</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.4576</v>
+        <v>-4.3927</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6778</v>
+        <v>-1.6904</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7798</v>
+        <v>-2.7023</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2487</v>
+        <v>-2.4974</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2487</v>
+        <v>2.2893</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8592</v>
+        <v>-0.3411</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0439</v>
+        <v>0.6844</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1847</v>
+        <v>-1.0255</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1675</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.1238</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>-0.4352</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.6577</v>
+        <v>-6.9458</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.762</v>
+        <v>-4.2262</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8957</v>
+        <v>-2.7196</v>
       </c>
       <c r="G10" t="n">
         <v>-5.4454</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7961</v>
+        <v>-1.0842</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9134</v>
+        <v>-0.3776</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8827</v>
+        <v>-0.7065</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.3497</v>
+        <v>-8.236000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.2014</v>
+        <v>-6.029</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1482</v>
+        <v>-2.207</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1853</v>
@@ -1312,13 +1312,13 @@
         <v>1.8731</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8592</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3295</v>
+        <v>-0.1571</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.5884</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7265</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-31.8367</v>
+        <v>-31.1841</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.6383</v>
+        <v>-10.9858</v>
       </c>
       <c r="F12" t="n">
-        <v>-20.1983</v>
+        <v>-20.1985</v>
       </c>
       <c r="G12" t="n">
         <v>-23.2071</v>
@@ -1390,13 +1390,13 @@
         <v>13.5277</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.648099999999999</v>
+        <v>-5.9957</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5402</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.1079</v>
+        <v>-5.108000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-1.981300000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.2974</v>
+        <v>7.3315</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5807</v>
+        <v>5.9378</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7167</v>
+        <v>1.3937</v>
       </c>
       <c r="G13" t="n">
         <v>3.4772</v>
@@ -1468,13 +1468,13 @@
         <v>1.4568</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0897</v>
+        <v>1.1238</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3602</v>
+        <v>0.7173</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7295</v>
+        <v>0.4065</v>
       </c>
       <c r="V13" t="n">
         <v>1.2737</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9104</v>
+        <v>6.2756</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5447</v>
+        <v>3.6162</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3657</v>
+        <v>2.6593</v>
       </c>
       <c r="G14" t="n">
         <v>4.482</v>
@@ -1546,13 +1546,13 @@
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9473</v>
+        <v>0.4179</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7177</v>
+        <v>0.3539</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2296</v>
+        <v>0.064</v>
       </c>
       <c r="V14" t="n">
         <v>1.1675</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. STRIKKER</t>
+          <t>J. SANTOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0431</v>
+        <v>3.5083</v>
       </c>
       <c r="E15" t="n">
-        <v>3.527</v>
+        <v>0.5869</v>
       </c>
       <c r="F15" t="n">
-        <v>0.516</v>
+        <v>2.9214</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2584</v>
+        <v>2.3721</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4988</v>
+        <v>0.9638</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7572</v>
+        <v>1.4083</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3037</v>
+        <v>0.9598</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.625</v>
+        <v>0.3026</v>
       </c>
       <c r="L15" t="n">
-        <v>4.9287</v>
+        <v>0.6572</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0453</v>
+        <v>1.4123</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1263</v>
+        <v>0.6612</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1716</v>
+        <v>0.7511</v>
       </c>
       <c r="P15" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5953</v>
+        <v>0.3037</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0746</v>
+        <v>0.6677</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5207000000000001</v>
+        <v>-0.364</v>
       </c>
       <c r="V15" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3181</v>
+        <v>3.369</v>
       </c>
       <c r="E16" t="n">
-        <v>1.787</v>
+        <v>2.4043</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5311</v>
+        <v>0.9648</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2713</v>
+        <v>2.3949</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7144</v>
+        <v>0.3114</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5569</v>
+        <v>2.0835</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8185</v>
+        <v>2.6564</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8738</v>
+        <v>1.324</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9447</v>
+        <v>1.3324</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5473</v>
+        <v>-0.2614</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1595</v>
+        <v>-1.0126</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3878</v>
+        <v>0.7511</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0812</v>
+        <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2768</v>
+        <v>0.6609</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0497</v>
+        <v>0.6615</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2271</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.23</v>
+        <v>0.9376</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X16" t="n">
         <v>-0.23</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2222</v>
+        <v>3.3181</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4043</v>
+        <v>1.787</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8179999999999999</v>
+        <v>1.5311</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3949</v>
+        <v>2.2713</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3114</v>
+        <v>0.7144</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0835</v>
+        <v>1.5569</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6564</v>
+        <v>2.8185</v>
       </c>
       <c r="K17" t="n">
-        <v>1.324</v>
+        <v>0.8738</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3324</v>
+        <v>1.9447</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2614</v>
+        <v>-0.5473</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0126</v>
+        <v>-0.1595</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7511</v>
+        <v>-0.3878</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5141</v>
+        <v>1.2768</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6615</v>
+        <v>1.0497</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1474</v>
+        <v>0.2271</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9376</v>
+        <v>-0.23</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-0.23</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SANTOS RODRÍGUEZ</t>
+          <t>M. STRIKKER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1472</v>
+        <v>3.039</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3726</v>
+        <v>2.6698</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7746</v>
+        <v>0.3692</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3721</v>
+        <v>2.2584</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9638</v>
+        <v>-1.4988</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4083</v>
+        <v>3.7572</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9598</v>
+        <v>3.3037</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3026</v>
+        <v>-1.625</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6572</v>
+        <v>4.9287</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4123</v>
+        <v>-1.0453</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6612</v>
+        <v>0.1263</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7511</v>
+        <v>-1.1716</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8325</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0574</v>
+        <v>1.5912</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4534</v>
+        <v>1.2173</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5108</v>
+        <v>0.3739</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2523</v>
+        <v>2.0086</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8771</v>
+        <v>1.6627</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3753</v>
+        <v>0.3459</v>
       </c>
       <c r="G19" t="n">
         <v>1.6762</v>
@@ -1936,13 +1936,13 @@
         <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7229</v>
+        <v>0.4792</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.382</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1266</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0.4776</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5354</v>
+        <v>1.9846</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7027</v>
+        <v>1.917</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1673</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>3.9284</v>
@@ -2014,13 +2014,13 @@
         <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4149</v>
+        <v>0.0343</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5748</v>
+        <v>-0.3605</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1599</v>
+        <v>0.3948</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9376</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1276</v>
+        <v>1.1055</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1838</v>
+        <v>0.7196</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9437</v>
+        <v>0.3859</v>
       </c>
       <c r="G21" t="n">
         <v>0.7531</v>
@@ -2092,13 +2092,13 @@
         <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8958</v>
+        <v>0.8738</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1181</v>
+        <v>0.4177</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0139</v>
+        <v>0.4561</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9376</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0171</v>
+        <v>-0.1037</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7816</v>
+        <v>-1.1031</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7645</v>
+        <v>0.9994</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4066</v>
@@ -2170,13 +2170,13 @@
         <v>0.4162</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0268</v>
+        <v>-0.1134</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3229</v>
+        <v>0.0014</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3497</v>
+        <v>-0.1148</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>31.8366</v>
+        <v>31.8365</v>
       </c>
       <c r="E23" t="n">
-        <v>20.1983</v>
+        <v>20.1982</v>
       </c>
       <c r="F23" t="n">
         <v>11.6383</v>
@@ -2221,7 +2221,7 @@
         <v>15.3284</v>
       </c>
       <c r="J23" t="n">
-        <v>24.90309999999999</v>
+        <v>24.9031</v>
       </c>
       <c r="K23" t="n">
         <v>9.432000000000002</v>
@@ -2236,10 +2236,10 @@
         <v>-1.5532</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1429000000000001</v>
+        <v>-0.1428999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.000199999999999978</v>
+        <v>-0.0001999999999997559</v>
       </c>
       <c r="Q23" t="n">
         <v>-13.5278</v>
@@ -2251,7 +2251,7 @@
         <v>6.6482</v>
       </c>
       <c r="T23" t="n">
-        <v>5.108</v>
+        <v>5.108000000000001</v>
       </c>
       <c r="U23" t="n">
         <v>1.5402</v>
